--- a/panchang-data/Mumbai2026.xlsx
+++ b/panchang-data/Mumbai2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dwivedi\Desktop\Base Files To Make New Panchang Excel Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyotishiji.com\Base Files To Make New Panchang Excel Files\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B9C39D-6568-4219-8B61-6A4C61EB8ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{583CD866-CD2A-47FA-8D3C-ABC213A12454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{E9866C55-5686-4BDD-BB77-50CABACCFD4D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{3C138C57-D9EB-4AEA-B0F5-03AD213703BB}"/>
   </bookViews>
   <sheets>
-    <sheet name="WORD_952" sheetId="1" r:id="rId1"/>
+    <sheet name="WORD_954" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WORD_952!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WORD_954!$A$1:$AB$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16634,7 +16634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DF6EDC-A466-480C-873B-63A59CC0636C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A71316-C137-479D-A230-AF691E8D0837}">
   <dimension ref="A1:AB366"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
@@ -48124,7 +48124,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB1" xr:uid="{06DF6EDC-A466-480C-873B-63A59CC0636C}"/>
+  <autoFilter ref="A1:AB1" xr:uid="{B7A71316-C137-479D-A230-AF691E8D0837}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/panchang-data/Mumbai2026.xlsx
+++ b/panchang-data/Mumbai2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5408">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16249,6 +16249,9 @@
   </si>
   <si>
     <t>121°05'03.40</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16738,7 +16741,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16824,7 +16827,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16910,7 +16913,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16996,7 +16999,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17082,7 +17085,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17168,7 +17171,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17254,7 +17257,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17340,7 +17343,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17426,7 +17429,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17512,7 +17515,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17598,7 +17601,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17684,7 +17687,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17770,7 +17773,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17856,7 +17859,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17942,7 +17945,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18028,7 +18031,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18114,7 +18117,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18200,7 +18203,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18286,7 +18289,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18372,7 +18375,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18458,7 +18461,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18544,7 +18547,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18630,7 +18633,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18716,7 +18719,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18802,7 +18805,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18888,7 +18891,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18974,7 +18977,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19060,7 +19063,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19146,7 +19149,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19232,7 +19235,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19318,7 +19321,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19404,7 +19407,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19490,7 +19493,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19576,7 +19579,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19662,7 +19665,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19748,7 +19751,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19834,7 +19837,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19920,7 +19923,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20006,7 +20009,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20092,7 +20095,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20178,7 +20181,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20264,7 +20267,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20350,7 +20353,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20436,7 +20439,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20522,7 +20525,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20608,7 +20611,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20694,7 +20697,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20780,7 +20783,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20866,7 +20869,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20952,7 +20955,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21038,7 +21041,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21124,7 +21127,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21210,7 +21213,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21296,7 +21299,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21382,7 +21385,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21468,7 +21471,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21554,7 +21557,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21640,7 +21643,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21726,7 +21729,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21812,7 +21815,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21898,7 +21901,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21984,7 +21987,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22070,7 +22073,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22156,7 +22159,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22242,7 +22245,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22328,7 +22331,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22414,7 +22417,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22500,7 +22503,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22586,7 +22589,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22672,7 +22675,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22758,7 +22761,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22844,7 +22847,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22930,7 +22933,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23016,7 +23019,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23102,7 +23105,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23188,7 +23191,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23274,7 +23277,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23360,7 +23363,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23446,7 +23449,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23532,7 +23535,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23618,7 +23621,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23704,7 +23707,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23790,7 +23793,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23876,7 +23879,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23962,7 +23965,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24048,7 +24051,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24134,7 +24137,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24220,7 +24223,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24306,7 +24309,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24392,7 +24395,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24478,7 +24481,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24564,7 +24567,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1009</v>
+        <v>1451</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24650,7 +24653,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24736,7 +24739,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24822,7 +24825,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24908,7 +24911,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24994,7 +24997,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25080,7 +25083,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25166,7 +25169,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25252,7 +25255,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25338,7 +25341,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25424,7 +25427,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25510,7 +25513,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25596,7 +25599,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25682,7 +25685,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25768,7 +25771,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25854,7 +25857,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25940,7 +25943,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26026,7 +26029,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26112,7 +26115,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26198,7 +26201,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26284,7 +26287,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26370,7 +26373,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26456,7 +26459,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26542,7 +26545,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26628,7 +26631,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26714,7 +26717,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26800,7 +26803,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26886,7 +26889,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26972,7 +26975,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27058,7 +27061,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1451</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27144,7 +27147,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27230,7 +27233,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27316,7 +27319,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27402,7 +27405,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27488,7 +27491,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27574,7 +27577,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27660,7 +27663,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27746,7 +27749,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27832,7 +27835,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27918,7 +27921,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -28004,7 +28007,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28090,7 +28093,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28176,7 +28179,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28262,7 +28265,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28348,7 +28351,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1876</v>
+        <v>2312</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28434,7 +28437,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28520,7 +28523,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28606,7 +28609,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28692,7 +28695,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28778,7 +28781,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28864,7 +28867,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28950,7 +28953,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29036,7 +29039,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29122,7 +29125,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29208,7 +29211,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29294,7 +29297,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29380,7 +29383,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29466,7 +29469,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29552,7 +29555,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29638,7 +29641,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1876</v>
+        <v>5407</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29724,7 +29727,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29810,7 +29813,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29896,7 +29899,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29982,7 +29985,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30068,7 +30071,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30154,7 +30157,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30240,7 +30243,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30326,7 +30329,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30412,7 +30415,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30498,7 +30501,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30584,7 +30587,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30670,7 +30673,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30756,7 +30759,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30842,7 +30845,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30928,7 +30931,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2312</v>
+        <v>5407</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
